--- a/Team-Data/2008-09/1-4-2008-09.xlsx
+++ b/Team-Data/2008-09/1-4-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -754,7 +821,7 @@
         <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ2" t="n">
         <v>24</v>
@@ -784,13 +851,13 @@
         <v>18</v>
       </c>
       <c r="AS2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT2" t="n">
         <v>18</v>
       </c>
       <c r="AU2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV2" t="n">
         <v>9</v>
@@ -799,7 +866,7 @@
         <v>23</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY2" t="n">
         <v>6</v>
@@ -808,7 +875,7 @@
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
         <v>15</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -846,94 +913,94 @@
         <v>34</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.824</v>
+        <v>0.853</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J3" t="n">
-        <v>75.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.484</v>
+        <v>0.485</v>
       </c>
       <c r="L3" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.371</v>
+        <v>0.373</v>
       </c>
       <c r="O3" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="P3" t="n">
-        <v>28</v>
+        <v>28.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.772</v>
+        <v>0.763</v>
       </c>
       <c r="R3" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S3" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="T3" t="n">
-        <v>43.3</v>
+        <v>43</v>
       </c>
       <c r="U3" t="n">
         <v>22.2</v>
       </c>
       <c r="V3" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W3" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
         <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="AB3" t="n">
         <v>101.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.2</v>
+        <v>10.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI3" t="n">
         <v>12</v>
@@ -948,25 +1015,25 @@
         <v>19</v>
       </c>
       <c r="AM3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AR3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AT3" t="n">
         <v>6</v>
@@ -981,10 +1048,10 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>26</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -1103,10 +1170,10 @@
         <v>-2.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF4" t="n">
         <v>23</v>
@@ -1115,7 +1182,7 @@
         <v>23</v>
       </c>
       <c r="AH4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1136,16 +1203,16 @@
         <v>18</v>
       </c>
       <c r="AO4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AP4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ4" t="n">
         <v>27</v>
       </c>
       <c r="AR4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS4" t="n">
         <v>29</v>
@@ -1157,7 +1224,7 @@
         <v>26</v>
       </c>
       <c r="AV4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW4" t="n">
         <v>20</v>
@@ -1169,7 +1236,7 @@
         <v>29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA4" t="n">
         <v>14</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -1207,127 +1274,127 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
         <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>0.394</v>
+        <v>0.412</v>
       </c>
       <c r="H5" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J5" t="n">
-        <v>84.40000000000001</v>
+        <v>84</v>
       </c>
       <c r="K5" t="n">
-        <v>0.44</v>
+        <v>0.442</v>
       </c>
       <c r="L5" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M5" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.384</v>
+        <v>0.385</v>
       </c>
       <c r="O5" t="n">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="P5" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.796</v>
+        <v>0.794</v>
       </c>
       <c r="R5" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
         <v>41.9</v>
       </c>
       <c r="U5" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="V5" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="W5" t="n">
         <v>7.4</v>
       </c>
       <c r="X5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>99.3</v>
+        <v>99.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>-4.3</v>
+        <v>-3.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="n">
         <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AH5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI5" t="n">
         <v>9</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK5" t="n">
         <v>23</v>
       </c>
       <c r="AL5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN5" t="n">
         <v>5</v>
       </c>
       <c r="AO5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP5" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AQ5" t="n">
         <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS5" t="n">
         <v>13</v>
@@ -1336,13 +1403,13 @@
         <v>13</v>
       </c>
       <c r="AU5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AV5" t="n">
         <v>18</v>
       </c>
       <c r="AW5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX5" t="n">
         <v>7</v>
@@ -1354,10 +1421,10 @@
         <v>23</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC5" t="n">
         <v>23</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -1404,70 +1471,70 @@
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.477</v>
+        <v>0.478</v>
       </c>
       <c r="L6" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M6" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="N6" t="n">
         <v>0.346</v>
       </c>
       <c r="O6" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="P6" t="n">
-        <v>25.1</v>
+        <v>25.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.766</v>
+        <v>0.769</v>
       </c>
       <c r="R6" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S6" t="n">
-        <v>30.8</v>
+        <v>31.1</v>
       </c>
       <c r="T6" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="U6" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W6" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X6" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.7</v>
+        <v>101.9</v>
       </c>
       <c r="AC6" t="n">
         <v>12.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1476,13 +1543,13 @@
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ6" t="n">
         <v>22</v>
@@ -1494,25 +1561,25 @@
         <v>9</v>
       </c>
       <c r="AM6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AN6" t="n">
         <v>20</v>
       </c>
       <c r="AO6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP6" t="n">
         <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
         <v>15</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT6" t="n">
         <v>12</v>
@@ -1527,16 +1594,16 @@
         <v>7</v>
       </c>
       <c r="AX6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BB6" t="n">
         <v>7</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -1571,70 +1638,70 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" t="n">
         <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>0.606</v>
+        <v>0.625</v>
       </c>
       <c r="H7" t="n">
         <v>48.5</v>
       </c>
       <c r="I7" t="n">
-        <v>37.6</v>
+        <v>37.8</v>
       </c>
       <c r="J7" t="n">
-        <v>83.5</v>
+        <v>83.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L7" t="n">
         <v>6.9</v>
       </c>
       <c r="M7" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0.335</v>
+        <v>0.336</v>
       </c>
       <c r="O7" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="P7" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.804</v>
+        <v>0.805</v>
       </c>
       <c r="R7" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S7" t="n">
-        <v>33.1</v>
+        <v>33.3</v>
       </c>
       <c r="T7" t="n">
-        <v>45</v>
+        <v>45.3</v>
       </c>
       <c r="U7" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="V7" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W7" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X7" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z7" t="n">
         <v>18.4</v>
@@ -1643,46 +1710,46 @@
         <v>19.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>99.3</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG7" t="n">
         <v>10</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>11</v>
       </c>
       <c r="AH7" t="n">
         <v>8</v>
       </c>
       <c r="AI7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ7" t="n">
         <v>7</v>
       </c>
       <c r="AK7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN7" t="n">
         <v>22</v>
       </c>
       <c r="AO7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP7" t="n">
         <v>29</v>
@@ -1691,7 +1758,7 @@
         <v>3</v>
       </c>
       <c r="AR7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
         <v>1</v>
@@ -1703,16 +1770,16 @@
         <v>10</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AX7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ7" t="n">
         <v>1</v>
@@ -1721,10 +1788,10 @@
         <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1928,7 @@
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1873,13 +1940,13 @@
         <v>18</v>
       </c>
       <c r="AR8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AT8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU8" t="n">
         <v>3</v>
@@ -1906,7 +1973,7 @@
         <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F9" t="n">
         <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>0.656</v>
+        <v>0.645</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
@@ -1953,49 +2020,49 @@
         <v>36.1</v>
       </c>
       <c r="J9" t="n">
-        <v>79.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0.456</v>
+        <v>0.458</v>
       </c>
       <c r="L9" t="n">
         <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.358</v>
+        <v>0.36</v>
       </c>
       <c r="O9" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="P9" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.759</v>
+        <v>0.758</v>
       </c>
       <c r="R9" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S9" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T9" t="n">
-        <v>40.8</v>
+        <v>40.6</v>
       </c>
       <c r="U9" t="n">
         <v>20.7</v>
       </c>
       <c r="V9" t="n">
-        <v>12.7</v>
+        <v>12.9</v>
       </c>
       <c r="W9" t="n">
         <v>7</v>
       </c>
       <c r="X9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y9" t="n">
         <v>4</v>
@@ -2004,19 +2071,19 @@
         <v>21.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>94.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC9" t="n">
         <v>1</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF9" t="n">
         <v>6</v>
@@ -2031,10 +2098,10 @@
         <v>17</v>
       </c>
       <c r="AJ9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AK9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AL9" t="n">
         <v>24</v>
@@ -2043,40 +2110,40 @@
         <v>27</v>
       </c>
       <c r="AN9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO9" t="n">
         <v>25</v>
       </c>
       <c r="AP9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ9" t="n">
         <v>19</v>
       </c>
       <c r="AR9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU9" t="n">
         <v>14</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>12</v>
       </c>
       <c r="AV9" t="n">
         <v>2</v>
       </c>
       <c r="AW9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX9" t="n">
         <v>9</v>
       </c>
       <c r="AY9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ9" t="n">
         <v>18</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -2198,10 +2265,10 @@
         <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG10" t="n">
         <v>25</v>
@@ -2246,10 +2313,10 @@
         <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW10" t="n">
         <v>5</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2456,7 @@
         <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI11" t="n">
         <v>29</v>
@@ -2419,16 +2486,16 @@
         <v>2</v>
       </c>
       <c r="AR11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV11" t="n">
         <v>13</v>
@@ -2437,7 +2504,7 @@
         <v>26</v>
       </c>
       <c r="AX11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY11" t="n">
         <v>23</v>
@@ -2449,10 +2516,10 @@
         <v>13</v>
       </c>
       <c r="BB11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>-2</v>
       </c>
       <c r="AD12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF12" t="n">
         <v>22</v>
@@ -2583,7 +2650,7 @@
         <v>14</v>
       </c>
       <c r="AL12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM12" t="n">
         <v>11</v>
@@ -2592,10 +2659,10 @@
         <v>17</v>
       </c>
       <c r="AO12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ12" t="n">
         <v>5</v>
@@ -2607,7 +2674,7 @@
         <v>2</v>
       </c>
       <c r="AT12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU12" t="n">
         <v>4</v>
@@ -2628,7 +2695,7 @@
         <v>27</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB12" t="n">
         <v>6</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -2663,25 +2730,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" t="n">
         <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G13" t="n">
-        <v>0.242</v>
+        <v>0.25</v>
       </c>
       <c r="H13" t="n">
         <v>48.9</v>
       </c>
       <c r="I13" t="n">
-        <v>35.4</v>
+        <v>35.6</v>
       </c>
       <c r="J13" t="n">
-        <v>83.7</v>
+        <v>84.2</v>
       </c>
       <c r="K13" t="n">
         <v>0.423</v>
@@ -2690,37 +2757,37 @@
         <v>5.1</v>
       </c>
       <c r="M13" t="n">
-        <v>16.4</v>
+        <v>16.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.308</v>
+        <v>0.305</v>
       </c>
       <c r="O13" t="n">
-        <v>17.6</v>
+        <v>17.3</v>
       </c>
       <c r="P13" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="Q13" t="n">
         <v>0.75</v>
       </c>
       <c r="R13" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="S13" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T13" t="n">
         <v>42.3</v>
       </c>
       <c r="U13" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="V13" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="W13" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X13" t="n">
         <v>6.4</v>
@@ -2729,19 +2796,19 @@
         <v>5.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="AA13" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>93.5</v>
+        <v>93.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>-6.3</v>
+        <v>-6.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AE13" t="n">
         <v>26</v>
@@ -2756,10 +2823,10 @@
         <v>1</v>
       </c>
       <c r="AI13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK13" t="n">
         <v>30</v>
@@ -2768,16 +2835,16 @@
         <v>23</v>
       </c>
       <c r="AM13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AN13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ13" t="n">
         <v>23</v>
@@ -2798,7 +2865,7 @@
         <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
@@ -2807,10 +2874,10 @@
         <v>22</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -2860,40 +2927,40 @@
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="J14" t="n">
-        <v>83.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="K14" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
       <c r="L14" t="n">
         <v>6.7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.3</v>
+        <v>18</v>
       </c>
       <c r="N14" t="n">
-        <v>0.369</v>
+        <v>0.373</v>
       </c>
       <c r="O14" t="n">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
       <c r="P14" t="n">
-        <v>28.3</v>
+        <v>27.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
       <c r="R14" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S14" t="n">
-        <v>32.3</v>
+        <v>32.5</v>
       </c>
       <c r="T14" t="n">
-        <v>44.6</v>
+        <v>44.9</v>
       </c>
       <c r="U14" t="n">
         <v>23.3</v>
@@ -2911,19 +2978,19 @@
         <v>4.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.6</v>
+        <v>107.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2932,7 +2999,7 @@
         <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
         <v>27</v>
@@ -2944,7 +3011,7 @@
         <v>6</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL14" t="n">
         <v>15</v>
@@ -2953,25 +3020,25 @@
         <v>14</v>
       </c>
       <c r="AN14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>14</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>6</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AT14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
@@ -2989,7 +3056,7 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -3027,61 +3094,61 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
         <v>23</v>
       </c>
       <c r="G15" t="n">
-        <v>0.324</v>
+        <v>0.303</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J15" t="n">
-        <v>78</v>
+        <v>77.8</v>
       </c>
       <c r="K15" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M15" t="n">
         <v>14.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0.332</v>
+        <v>0.328</v>
       </c>
       <c r="O15" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P15" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.756</v>
+        <v>0.752</v>
       </c>
       <c r="R15" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S15" t="n">
         <v>28.5</v>
       </c>
       <c r="T15" t="n">
-        <v>38.6</v>
+        <v>38.5</v>
       </c>
       <c r="U15" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="V15" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="W15" t="n">
         <v>7.4</v>
@@ -3090,22 +3157,22 @@
         <v>4.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>94.40000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>-4.9</v>
+        <v>-5.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AE15" t="n">
         <v>24</v>
@@ -3117,7 +3184,7 @@
         <v>24</v>
       </c>
       <c r="AH15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI15" t="n">
         <v>27</v>
@@ -3135,10 +3202,10 @@
         <v>26</v>
       </c>
       <c r="AN15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP15" t="n">
         <v>12</v>
@@ -3150,7 +3217,7 @@
         <v>26</v>
       </c>
       <c r="AS15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT15" t="n">
         <v>30</v>
@@ -3162,22 +3229,22 @@
         <v>16</v>
       </c>
       <c r="AW15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX15" t="n">
         <v>22</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA15" t="n">
         <v>9</v>
       </c>
       <c r="BB15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BC15" t="n">
         <v>24</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>15</v>
@@ -3299,7 +3366,7 @@
         <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI16" t="n">
         <v>22</v>
@@ -3323,7 +3390,7 @@
         <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ16" t="n">
         <v>29</v>
@@ -3335,7 +3402,7 @@
         <v>20</v>
       </c>
       <c r="AT16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU16" t="n">
         <v>25</v>
@@ -3356,7 +3423,7 @@
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB16" t="n">
         <v>22</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G17" t="n">
-        <v>0.471</v>
+        <v>0.457</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
@@ -3409,25 +3476,25 @@
         <v>35.9</v>
       </c>
       <c r="J17" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.333</v>
+        <v>0.335</v>
       </c>
       <c r="O17" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="P17" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q17" t="n">
         <v>0.776</v>
@@ -3436,19 +3503,19 @@
         <v>12.6</v>
       </c>
       <c r="S17" t="n">
-        <v>30.9</v>
+        <v>30.6</v>
       </c>
       <c r="T17" t="n">
-        <v>43.5</v>
+        <v>43.2</v>
       </c>
       <c r="U17" t="n">
         <v>20.6</v>
       </c>
       <c r="V17" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="W17" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X17" t="n">
         <v>3.6</v>
@@ -3457,31 +3524,31 @@
         <v>5</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="AB17" t="n">
-        <v>96.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI17" t="n">
         <v>23</v>
@@ -3493,46 +3560,46 @@
         <v>25</v>
       </c>
       <c r="AL17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM17" t="n">
         <v>25</v>
       </c>
       <c r="AN17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO17" t="n">
         <v>9</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR17" t="n">
         <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU17" t="n">
         <v>15</v>
       </c>
       <c r="AV17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX17" t="n">
         <v>28</v>
       </c>
       <c r="AY17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3718,22 @@
         <v>-6</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
         <v>26</v>
       </c>
       <c r="AF18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH18" t="n">
         <v>5</v>
       </c>
       <c r="AI18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AJ18" t="n">
         <v>8</v>
@@ -3675,19 +3742,19 @@
         <v>29</v>
       </c>
       <c r="AL18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM18" t="n">
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ18" t="n">
         <v>17</v>
@@ -3720,7 +3787,7 @@
         <v>24</v>
       </c>
       <c r="BA18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB18" t="n">
         <v>19</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -3848,7 +3915,7 @@
         <v>4</v>
       </c>
       <c r="AI19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ19" t="n">
         <v>12</v>
@@ -3860,10 +3927,10 @@
         <v>6</v>
       </c>
       <c r="AM19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO19" t="n">
         <v>5</v>
@@ -3875,7 +3942,7 @@
         <v>9</v>
       </c>
       <c r="AR19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS19" t="n">
         <v>21</v>
@@ -3905,7 +3972,7 @@
         <v>11</v>
       </c>
       <c r="BB19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BC19" t="n">
         <v>19</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4085,7 @@
         <v>30</v>
       </c>
       <c r="AE20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF20" t="n">
         <v>5</v>
@@ -4066,10 +4133,10 @@
         <v>29</v>
       </c>
       <c r="AU20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW20" t="n">
         <v>8</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -4119,100 +4186,100 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F21" t="n">
         <v>19</v>
       </c>
       <c r="G21" t="n">
-        <v>0.406</v>
+        <v>0.387</v>
       </c>
       <c r="H21" t="n">
         <v>48.2</v>
       </c>
       <c r="I21" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J21" t="n">
-        <v>86.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="K21" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L21" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="M21" t="n">
-        <v>29.1</v>
+        <v>29.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="O21" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="P21" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.798</v>
+        <v>0.797</v>
       </c>
       <c r="R21" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T21" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U21" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V21" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="W21" t="n">
         <v>7.4</v>
       </c>
       <c r="X21" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA21" t="n">
         <v>19.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>104.1</v>
+        <v>104.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3.1</v>
+        <v>-3.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AH21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ21" t="n">
         <v>1</v>
@@ -4227,34 +4294,34 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ21" t="n">
         <v>6</v>
       </c>
       <c r="AR21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
         <v>7</v>
       </c>
       <c r="AT21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4266,7 +4333,7 @@
         <v>7</v>
       </c>
       <c r="BA21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB21" t="n">
         <v>3</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-8.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>30</v>
@@ -4448,7 +4515,7 @@
         <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB22" t="n">
         <v>27</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -4483,85 +4550,85 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E23" t="n">
         <v>26</v>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
-        <v>0.765</v>
+        <v>0.788</v>
       </c>
       <c r="H23" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="I23" t="n">
         <v>36</v>
       </c>
       <c r="J23" t="n">
-        <v>78.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="K23" t="n">
         <v>0.456</v>
       </c>
       <c r="L23" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>26</v>
+        <v>25.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0.381</v>
+        <v>0.378</v>
       </c>
       <c r="O23" t="n">
         <v>18.7</v>
       </c>
       <c r="P23" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="Q23" t="n">
         <v>0.71</v>
       </c>
       <c r="R23" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S23" t="n">
-        <v>32.3</v>
+        <v>32.6</v>
       </c>
       <c r="T23" t="n">
-        <v>42.5</v>
+        <v>42.8</v>
       </c>
       <c r="U23" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="V23" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W23" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X23" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Y23" t="n">
         <v>4</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>100.6</v>
+        <v>100.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AE23" t="n">
         <v>3</v>
@@ -4573,16 +4640,16 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
         <v>19</v>
       </c>
       <c r="AJ23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL23" t="n">
         <v>2</v>
@@ -4591,10 +4658,10 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP23" t="n">
         <v>7</v>
@@ -4603,13 +4670,13 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AT23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU23" t="n">
         <v>28</v>
@@ -4621,7 +4688,7 @@
         <v>11</v>
       </c>
       <c r="AX23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY23" t="n">
         <v>4</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-1.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
         <v>19</v>
@@ -4752,7 +4819,7 @@
         <v>19</v>
       </c>
       <c r="AG24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH24" t="n">
         <v>23</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP24" t="n">
         <v>15</v>
@@ -4791,19 +4858,19 @@
         <v>12</v>
       </c>
       <c r="AT24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU24" t="n">
         <v>18</v>
       </c>
       <c r="AV24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW24" t="n">
         <v>9</v>
       </c>
       <c r="AX24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY24" t="n">
         <v>21</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4934,7 +5001,7 @@
         <v>9</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
         <v>20</v>
@@ -4973,7 +5040,7 @@
         <v>9</v>
       </c>
       <c r="AT25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU25" t="n">
         <v>11</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -5044,91 +5111,91 @@
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J26" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L26" t="n">
         <v>7.8</v>
       </c>
       <c r="M26" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0.382</v>
+        <v>0.386</v>
       </c>
       <c r="O26" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="P26" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.775</v>
+        <v>0.777</v>
       </c>
       <c r="R26" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="S26" t="n">
-        <v>27.6</v>
+        <v>27.8</v>
       </c>
       <c r="T26" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U26" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V26" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W26" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X26" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y26" t="n">
         <v>3.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.59999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI26" t="n">
         <v>14</v>
       </c>
       <c r="AJ26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL26" t="n">
         <v>5</v>
@@ -5137,16 +5204,16 @@
         <v>8</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AO26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5158,25 +5225,25 @@
         <v>19</v>
       </c>
       <c r="AU26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AV26" t="n">
         <v>3</v>
       </c>
       <c r="AW26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB26" t="n">
         <v>14</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
@@ -5301,7 +5368,7 @@
         <v>28</v>
       </c>
       <c r="AH27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI27" t="n">
         <v>21</v>
@@ -5331,7 +5398,7 @@
         <v>8</v>
       </c>
       <c r="AR27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS27" t="n">
         <v>26</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5483,7 +5550,7 @@
         <v>5</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI28" t="n">
         <v>10</v>
@@ -5498,7 +5565,7 @@
         <v>3</v>
       </c>
       <c r="AM28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -5575,70 +5642,70 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F29" t="n">
         <v>20</v>
       </c>
       <c r="G29" t="n">
-        <v>0.412</v>
+        <v>0.394</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>35.8</v>
+        <v>35.6</v>
       </c>
       <c r="J29" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K29" t="n">
-        <v>0.452</v>
+        <v>0.45</v>
       </c>
       <c r="L29" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M29" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="N29" t="n">
-        <v>0.377</v>
+        <v>0.38</v>
       </c>
       <c r="O29" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="P29" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.83</v>
+        <v>0.826</v>
       </c>
       <c r="R29" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T29" t="n">
         <v>39.3</v>
       </c>
       <c r="U29" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V29" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W29" t="n">
         <v>6.5</v>
       </c>
       <c r="X29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z29" t="n">
         <v>19.1</v>
@@ -5647,22 +5714,22 @@
         <v>20.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>97</v>
+        <v>96.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.7</v>
+        <v>-3</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AE29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF29" t="n">
         <v>19</v>
       </c>
       <c r="AG29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH29" t="n">
         <v>17</v>
@@ -5674,19 +5741,19 @@
         <v>18</v>
       </c>
       <c r="AK29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP29" t="n">
         <v>24</v>
@@ -5698,34 +5765,34 @@
         <v>29</v>
       </c>
       <c r="AS29" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT29" t="n">
         <v>27</v>
       </c>
       <c r="AU29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV29" t="n">
         <v>8</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>7</v>
       </c>
       <c r="AW29" t="n">
         <v>28</v>
       </c>
       <c r="AX29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ29" t="n">
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC29" t="n">
         <v>21</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>2.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
         <v>13</v>
@@ -5847,16 +5914,16 @@
         <v>15</v>
       </c>
       <c r="AH30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI30" t="n">
         <v>6</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>5</v>
       </c>
       <c r="AJ30" t="n">
         <v>16</v>
       </c>
       <c r="AK30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL30" t="n">
         <v>28</v>
@@ -5865,7 +5932,7 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
@@ -5874,7 +5941,7 @@
         <v>6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
         <v>7</v>
@@ -5895,7 +5962,7 @@
         <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY30" t="n">
         <v>17</v>
@@ -5910,7 +5977,7 @@
         <v>10</v>
       </c>
       <c r="BC30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
@@ -5939,100 +6006,100 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
         <v>25</v>
       </c>
       <c r="G31" t="n">
-        <v>0.219</v>
+        <v>0.194</v>
       </c>
       <c r="H31" t="n">
         <v>48.2</v>
       </c>
       <c r="I31" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J31" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="M31" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="N31" t="n">
-        <v>0.305</v>
+        <v>0.307</v>
       </c>
       <c r="O31" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P31" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q31" t="n">
         <v>0.75</v>
       </c>
       <c r="R31" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="S31" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="T31" t="n">
-        <v>40.5</v>
+        <v>40.1</v>
       </c>
       <c r="U31" t="n">
-        <v>20.5</v>
+        <v>20.8</v>
       </c>
       <c r="V31" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="W31" t="n">
         <v>7.5</v>
       </c>
       <c r="X31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="AA31" t="n">
         <v>19.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>94.2</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-6.5</v>
+        <v>-6.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI31" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AJ31" t="n">
         <v>9</v>
@@ -6044,10 +6111,10 @@
         <v>22</v>
       </c>
       <c r="AM31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO31" t="n">
         <v>29</v>
@@ -6059,22 +6126,22 @@
         <v>22</v>
       </c>
       <c r="AR31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AU31" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AV31" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AW31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX31" t="n">
         <v>25</v>
@@ -6083,13 +6150,13 @@
         <v>18</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA31" t="n">
         <v>28</v>
       </c>
       <c r="BB31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BC31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-4-2008-09</t>
+          <t>2009-01-04</t>
         </is>
       </c>
     </row>
